--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -368,7 +368,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -618,7 +618,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -645,7 +645,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/analysis_uuid</t>
+    <t>http://openelis-global.org/analysis_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -718,7 +718,7 @@
     <t>ServiceRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -761,7 +761,7 @@
     <t>ServiceRequest.identifier:labNo.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/samp_labNo</t>
+    <t>http://openelis-global.org/samp_labNo</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:labNo.value</t>
@@ -776,7 +776,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -820,7 +820,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -846,7 +846,7 @@
 priorrenewed order</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -980,7 +980,7 @@
     <t>Classification of the requested service.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>ObservationHistory.value</t>
@@ -1072,7 +1072,7 @@
     <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred].</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1290,7 +1290,7 @@
     <t>Codified order entry details which are based on order context.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1357,7 +1357,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1430,7 +1430,7 @@
     <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1528,7 +1528,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1550,7 +1550,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1593,7 +1593,7 @@
     <t>ServiceRequest.locationReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1621,7 +1621,7 @@
     <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1639,7 +1639,7 @@
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1664,7 +1664,7 @@
     <t>ServiceRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1690,7 +1690,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1759,7 +1759,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1805,7 +1805,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2128,7 +2128,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.37890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="126.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-service-request.xlsx
+++ b/StructureDefinition-openelis-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
